--- a/isms-core-framework/A.5-organisational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/ISMS-IMP-A.5.31.1_Regulatory_Inventory_20260301.xlsx
+++ b/isms-core-framework/A.5-organisational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/ISMS-IMP-A.5.31.1_Regulatory_Inventory_20260301.xlsx
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="P3" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="4">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="P4" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="5">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="P5" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="6">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="P6" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="7">
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="P7" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="8">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="P8" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="9">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="P9" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
     <row r="10">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="P10" s="14" t="n">
-        <v>46082.50844222181</v>
+        <v>46082.74821694789</v>
       </c>
     </row>
   </sheetData>
